--- a/Excel/MonsterBabelConfig.xlsx
+++ b/Excel/MonsterBabelConfig.xlsx
@@ -30,15 +30,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="46">
   <si>
     <t>ID</t>
   </si>
   <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Name</t>
+    <t>Layer</t>
   </si>
   <si>
     <t>StartLevel</t>
@@ -47,13 +44,67 @@
     <t>EndLevel</t>
   </si>
   <si>
-    <t>SkillIdList</t>
-  </si>
-  <si>
-    <t>AttrRate</t>
-  </si>
-  <si>
-    <t>RuneCount</t>
+    <t>Atk</t>
+  </si>
+  <si>
+    <t>RiseAtk</t>
+  </si>
+  <si>
+    <t>Def</t>
+  </si>
+  <si>
+    <t>RiseDef</t>
+  </si>
+  <si>
+    <t>Hp</t>
+  </si>
+  <si>
+    <t>RiseHp</t>
+  </si>
+  <si>
+    <t>DamageMul</t>
+  </si>
+  <si>
+    <t>MulRise</t>
+  </si>
+  <si>
+    <t>MulResist</t>
+  </si>
+  <si>
+    <t>MulResistRise</t>
+  </si>
+  <si>
+    <t>DamageIncrea</t>
+  </si>
+  <si>
+    <t>DamageResist</t>
+  </si>
+  <si>
+    <t>CritRate</t>
+  </si>
+  <si>
+    <t>CritDamage</t>
+  </si>
+  <si>
+    <t>Accuracy</t>
+  </si>
+  <si>
+    <t>RiseAccuracy</t>
+  </si>
+  <si>
+    <t>Miss</t>
+  </si>
+  <si>
+    <t>RiseMiss</t>
+  </si>
+  <si>
+    <t>Lucky</t>
+  </si>
+  <si>
+    <t>Curse</t>
+  </si>
+  <si>
+    <t>Speed</t>
   </si>
   <si>
     <t>Id</t>
@@ -65,46 +116,58 @@
     <t>string</t>
   </si>
   <si>
-    <t>int[]</t>
-  </si>
-  <si>
     <t>double</t>
   </si>
   <si>
-    <t>通天侍卫</t>
-  </si>
-  <si>
-    <t>1001,1002</t>
-  </si>
-  <si>
-    <t>通天祭司</t>
-  </si>
-  <si>
-    <t>1001,1002,2002,3003</t>
-  </si>
-  <si>
-    <t>通天主教</t>
-  </si>
-  <si>
-    <t>2002,2003,2005,2007,2010,3008,1004</t>
-  </si>
-  <si>
-    <t>2001,2002</t>
-  </si>
-  <si>
-    <t>1001,1002,2002,3003,1005</t>
-  </si>
-  <si>
-    <t>2002,2003,2005,2007,2010,3008,1004,1005</t>
-  </si>
-  <si>
-    <t>2002</t>
-  </si>
-  <si>
-    <t>1002,1004,1005</t>
-  </si>
-  <si>
-    <t>2002,2003,2005,2007,2010,3008,1012,2012</t>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>0.1</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>5E+4</t>
+  </si>
+  <si>
+    <t>0.2</t>
+  </si>
+  <si>
+    <t>30000</t>
+  </si>
+  <si>
+    <t>6000</t>
+  </si>
+  <si>
+    <t>1E+6</t>
+  </si>
+  <si>
+    <t>0.3</t>
+  </si>
+  <si>
+    <t>1000000</t>
+  </si>
+  <si>
+    <t>200000</t>
+  </si>
+  <si>
+    <t>6E+8</t>
+  </si>
+  <si>
+    <t>0.4</t>
+  </si>
+  <si>
+    <t>80000000</t>
+  </si>
+  <si>
+    <t>16000000</t>
+  </si>
+  <si>
+    <t>5E+10</t>
+  </si>
+  <si>
+    <t>0.5</t>
   </si>
 </sst>
 </file>
@@ -739,14 +802,20 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1066,601 +1135,636 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1"/>
+  <dimension ref="C1:AA15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="8" style="2" customWidth="1"/>
-    <col min="3" max="7" width="9.875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="34.875" style="2" customWidth="1"/>
-    <col min="9" max="10" width="26.75" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="8.58333333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="4.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="7.25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.1666666666667" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.9166666666667" style="3" customWidth="1"/>
+    <col min="8" max="8" width="8.41666666666667" style="3" customWidth="1"/>
+    <col min="9" max="9" width="10.3333333333333" style="3" customWidth="1"/>
+    <col min="10" max="10" width="10.1666666666667" style="3" customWidth="1"/>
+    <col min="11" max="11" width="15.8333333333333" style="3" customWidth="1"/>
+    <col min="12" max="12" width="9.58333333333333" style="3" customWidth="1"/>
+    <col min="13" max="13" width="10.1666666666667" style="3" customWidth="1"/>
+    <col min="14" max="14" width="9.08333333333333" style="3" customWidth="1"/>
+    <col min="15" max="16" width="12.1666666666667" style="1" customWidth="1"/>
+    <col min="17" max="17" width="12" style="1" customWidth="1"/>
+    <col min="18" max="18" width="12.1666666666667" style="1" customWidth="1"/>
+    <col min="19" max="19" width="6.375" style="1" customWidth="1"/>
+    <col min="20" max="20" width="10" style="1" customWidth="1"/>
+    <col min="21" max="21" width="9.08333333333333" style="1" customWidth="1"/>
+    <col min="22" max="22" width="9" style="1" customWidth="1"/>
+    <col min="23" max="23" width="7.25" style="1" customWidth="1"/>
+    <col min="24" max="24" width="10.5" style="1" customWidth="1"/>
+    <col min="25" max="26" width="6.33333333333333" style="1" customWidth="1"/>
+    <col min="27" max="27" width="8.375" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
+    <row r="1" s="1" customFormat="1" customHeight="1"/>
+    <row r="2" s="1" customFormat="1" customHeight="1"/>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:27">
+      <c r="C3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="U3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="W3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="X3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA3" s="4" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:27">
+      <c r="C4" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="R4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="T4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="U4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="W4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="X4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA4" s="4" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3" t="s">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:27">
+      <c r="C5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="S5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="T5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="U5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="V5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="W5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="X5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA5" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:27">
+      <c r="C6" s="2">
         <v>1</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>200</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M6" s="2">
+        <v>0</v>
+      </c>
+      <c r="N6" s="2">
+        <v>0</v>
+      </c>
+      <c r="O6" s="2">
+        <v>0</v>
+      </c>
+      <c r="P6" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2">
+        <v>0</v>
+      </c>
+      <c r="S6" s="2">
+        <v>0</v>
+      </c>
+      <c r="T6" s="2">
+        <v>0</v>
+      </c>
+      <c r="U6" s="2">
+        <v>5</v>
+      </c>
+      <c r="V6" s="2">
+        <v>0</v>
+      </c>
+      <c r="W6" s="2">
+        <v>5</v>
+      </c>
+      <c r="X6" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="2">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:27">
+      <c r="C7" s="2">
         <v>2</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="D7" s="2">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2">
+        <f t="shared" ref="E7:E9" si="0">F6+1</f>
+        <v>201</v>
+      </c>
+      <c r="F7" s="2">
+        <v>400</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="M7" s="2">
+        <v>0</v>
+      </c>
+      <c r="N7" s="2">
+        <v>0</v>
+      </c>
+      <c r="O7" s="2">
+        <v>0</v>
+      </c>
+      <c r="P7" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>0</v>
+      </c>
+      <c r="R7" s="2">
+        <v>0</v>
+      </c>
+      <c r="S7" s="2">
+        <v>0</v>
+      </c>
+      <c r="T7" s="2">
+        <v>0</v>
+      </c>
+      <c r="U7" s="2">
+        <v>10</v>
+      </c>
+      <c r="V7" s="2">
+        <v>0</v>
+      </c>
+      <c r="W7" s="2">
+        <v>10</v>
+      </c>
+      <c r="X7" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="2">
+        <v>2</v>
+      </c>
+      <c r="Z7" s="2">
+        <v>2</v>
+      </c>
+      <c r="AA7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="3:27">
+      <c r="C8" s="2">
         <v>3</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2">
+        <f t="shared" si="0"/>
+        <v>401</v>
+      </c>
+      <c r="F8" s="2">
+        <v>600</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="M8" s="2">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2">
+        <v>0</v>
+      </c>
+      <c r="O8" s="2">
+        <v>0</v>
+      </c>
+      <c r="P8" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>0</v>
+      </c>
+      <c r="R8" s="2">
+        <v>0</v>
+      </c>
+      <c r="S8" s="2">
+        <v>0</v>
+      </c>
+      <c r="T8" s="2">
+        <v>0</v>
+      </c>
+      <c r="U8" s="2">
+        <v>15</v>
+      </c>
+      <c r="V8" s="2">
+        <v>0</v>
+      </c>
+      <c r="W8" s="2">
+        <v>15</v>
+      </c>
+      <c r="X8" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="2">
+        <v>3</v>
+      </c>
+      <c r="Z8" s="2">
+        <v>3</v>
+      </c>
+      <c r="AA8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="3:27">
+      <c r="C9" s="2">
         <v>4</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>7</v>
+      <c r="D9" s="2">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2">
+        <f t="shared" si="0"/>
+        <v>601</v>
+      </c>
+      <c r="F9" s="2">
+        <v>10000</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="M9" s="2">
+        <v>0</v>
+      </c>
+      <c r="N9" s="2">
+        <v>0</v>
+      </c>
+      <c r="O9" s="2">
+        <v>0</v>
+      </c>
+      <c r="P9" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>0</v>
+      </c>
+      <c r="R9" s="2">
+        <v>0</v>
+      </c>
+      <c r="S9" s="2">
+        <v>0</v>
+      </c>
+      <c r="T9" s="2">
+        <v>0</v>
+      </c>
+      <c r="U9" s="2">
+        <v>20</v>
+      </c>
+      <c r="V9" s="2">
+        <v>0</v>
+      </c>
+      <c r="W9" s="2">
+        <v>20</v>
+      </c>
+      <c r="X9" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="2">
+        <v>4</v>
+      </c>
+      <c r="Z9" s="2">
+        <v>4</v>
+      </c>
+      <c r="AA9" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>7</v>
-      </c>
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:27">
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>9</v>
-      </c>
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="3:27">
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
     </row>
-    <row r="6" customHeight="1" spans="3:10">
-      <c r="C6" s="1">
-        <v>1</v>
-      </c>
-      <c r="D6" s="1">
-        <v>1</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="1">
-        <v>1</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1000</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="4">
-        <v>1</v>
-      </c>
-      <c r="J6" s="5">
-        <v>4</v>
-      </c>
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="3:27">
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
     </row>
-    <row r="7" customHeight="1" spans="3:10">
-      <c r="C7" s="1">
-        <v>2</v>
-      </c>
-      <c r="D7" s="1">
-        <v>2</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="1">
-        <v>1</v>
-      </c>
-      <c r="G7" s="1">
-        <v>1000</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="I7" s="4">
-        <v>2</v>
-      </c>
-      <c r="J7" s="5">
-        <v>4</v>
-      </c>
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="3:27">
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
     </row>
-    <row r="8" customHeight="1" spans="3:10">
-      <c r="C8" s="1">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1">
-        <v>3</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="1">
-        <v>1</v>
-      </c>
-      <c r="G8" s="1">
-        <v>1000</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I8" s="4">
-        <v>3</v>
-      </c>
-      <c r="J8" s="5">
-        <v>4</v>
-      </c>
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="3:27">
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
     </row>
-    <row r="9" customHeight="1" spans="3:10">
-      <c r="C9" s="1">
-        <v>4</v>
-      </c>
-      <c r="D9" s="1">
-        <v>1</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="1">
-        <f t="shared" ref="F9:F23" si="0">G6+1</f>
-        <v>1001</v>
-      </c>
-      <c r="G9" s="1">
-        <v>2000</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="I9" s="4">
-        <v>1</v>
-      </c>
-      <c r="J9" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="3:10">
-      <c r="C10" s="1">
-        <v>5</v>
-      </c>
-      <c r="D10" s="1">
-        <v>2</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" s="1">
-        <f t="shared" si="0"/>
-        <v>1001</v>
-      </c>
-      <c r="G10" s="1">
-        <v>2000</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="I10" s="4">
-        <v>2</v>
-      </c>
-      <c r="J10" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="3:10">
-      <c r="C11" s="1">
-        <v>6</v>
-      </c>
-      <c r="D11" s="1">
-        <v>3</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" s="1">
-        <f t="shared" si="0"/>
-        <v>1001</v>
-      </c>
-      <c r="G11" s="1">
-        <v>2000</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I11" s="4">
-        <v>3</v>
-      </c>
-      <c r="J11" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="3:10">
-      <c r="C12" s="1">
-        <v>7</v>
-      </c>
-      <c r="D12" s="1">
-        <v>1</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="1">
-        <f t="shared" si="0"/>
-        <v>2001</v>
-      </c>
-      <c r="G12" s="1">
-        <v>5000</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I12" s="4">
-        <v>1</v>
-      </c>
-      <c r="J12" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="3:10">
-      <c r="C13" s="1">
-        <v>8</v>
-      </c>
-      <c r="D13" s="1">
-        <v>2</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F13" s="1">
-        <f t="shared" si="0"/>
-        <v>2001</v>
-      </c>
-      <c r="G13" s="1">
-        <v>5000</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="I13" s="4">
-        <v>2</v>
-      </c>
-      <c r="J13" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="3:10">
-      <c r="C14" s="1">
-        <v>9</v>
-      </c>
-      <c r="D14" s="1">
-        <v>3</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F14" s="1">
-        <f t="shared" si="0"/>
-        <v>2001</v>
-      </c>
-      <c r="G14" s="1">
-        <v>5000</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I14" s="4">
-        <v>3</v>
-      </c>
-      <c r="J14" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="3:10">
-      <c r="C15" s="1">
-        <v>10</v>
-      </c>
-      <c r="D15" s="1">
-        <v>1</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15" s="1">
-        <f t="shared" si="0"/>
-        <v>5001</v>
-      </c>
-      <c r="G15" s="1">
-        <v>10000</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="I15" s="4">
-        <v>1</v>
-      </c>
-      <c r="J15" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="3:10">
-      <c r="C16" s="1">
-        <v>11</v>
-      </c>
-      <c r="D16" s="1">
-        <v>2</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F16" s="1">
-        <f t="shared" si="0"/>
-        <v>5001</v>
-      </c>
-      <c r="G16" s="1">
-        <v>10000</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="I16" s="4">
-        <v>2</v>
-      </c>
-      <c r="J16" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="3:10">
-      <c r="C17" s="1">
-        <v>12</v>
-      </c>
-      <c r="D17" s="1">
-        <v>3</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F17" s="1">
-        <f t="shared" si="0"/>
-        <v>5001</v>
-      </c>
-      <c r="G17" s="1">
-        <v>10000</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I17" s="4">
-        <v>3</v>
-      </c>
-      <c r="J17" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="3:10">
-      <c r="C18" s="1">
-        <v>13</v>
-      </c>
-      <c r="D18" s="1">
-        <v>1</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18" s="1">
-        <f t="shared" si="0"/>
-        <v>10001</v>
-      </c>
-      <c r="G18" s="1">
-        <v>45000</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="I18" s="4">
-        <v>1</v>
-      </c>
-      <c r="J18" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="3:10">
-      <c r="C19" s="1">
-        <v>14</v>
-      </c>
-      <c r="D19" s="1">
-        <v>2</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F19" s="1">
-        <f t="shared" si="0"/>
-        <v>10001</v>
-      </c>
-      <c r="G19" s="1">
-        <v>45000</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="I19" s="4">
-        <v>2</v>
-      </c>
-      <c r="J19" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="3:10">
-      <c r="C20" s="1">
-        <v>15</v>
-      </c>
-      <c r="D20" s="1">
-        <v>3</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F20" s="1">
-        <f t="shared" si="0"/>
-        <v>10001</v>
-      </c>
-      <c r="G20" s="1">
-        <v>45000</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I20" s="4">
-        <v>3</v>
-      </c>
-      <c r="J20" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="3:10">
-      <c r="C21" s="1">
-        <v>16</v>
-      </c>
-      <c r="D21" s="1">
-        <v>1</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F21" s="1">
-        <f t="shared" si="0"/>
-        <v>45001</v>
-      </c>
-      <c r="G21" s="1">
-        <v>200000</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I21" s="4">
-        <v>1</v>
-      </c>
-      <c r="J21" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="3:10">
-      <c r="C22" s="1">
-        <v>17</v>
-      </c>
-      <c r="D22" s="1">
-        <v>2</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F22" s="1">
-        <f t="shared" si="0"/>
-        <v>45001</v>
-      </c>
-      <c r="G22" s="1">
-        <v>200000</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I22" s="4">
-        <v>2</v>
-      </c>
-      <c r="J22" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="3:10">
-      <c r="C23" s="1">
-        <v>18</v>
-      </c>
-      <c r="D23" s="1">
-        <v>3</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F23" s="1">
-        <f t="shared" si="0"/>
-        <v>45001</v>
-      </c>
-      <c r="G23" s="1">
-        <v>200000</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="I23" s="4">
-        <v>3</v>
-      </c>
-      <c r="J23" s="2">
-        <v>10</v>
-      </c>
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="3:27">
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C5:J5 J3:J4 C3:I4" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:AA5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/MonsterBabelConfig.xlsx
+++ b/Excel/MonsterBabelConfig.xlsx
@@ -128,7 +128,7 @@
     <t>200</t>
   </si>
   <si>
-    <t>5E+4</t>
+    <t>5E+5</t>
   </si>
   <si>
     <t>0.2</t>
@@ -140,7 +140,7 @@
     <t>6000</t>
   </si>
   <si>
-    <t>1E+6</t>
+    <t>1E+7</t>
   </si>
   <si>
     <t>0.3</t>
@@ -152,7 +152,7 @@
     <t>200000</t>
   </si>
   <si>
-    <t>6E+8</t>
+    <t>6E+9</t>
   </si>
   <si>
     <t>0.4</t>
@@ -164,7 +164,7 @@
     <t>16000000</t>
   </si>
   <si>
-    <t>5E+10</t>
+    <t>5E+11</t>
   </si>
   <si>
     <t>0.5</t>

--- a/Excel/MonsterBabelConfig.xlsx
+++ b/Excel/MonsterBabelConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="37">
   <si>
     <t>ID</t>
   </si>
@@ -62,30 +62,30 @@
     <t>RiseHp</t>
   </si>
   <si>
-    <t>DamageMul</t>
-  </si>
-  <si>
-    <t>MulRise</t>
-  </si>
-  <si>
-    <t>MulResist</t>
-  </si>
-  <si>
-    <t>MulResistRise</t>
-  </si>
-  <si>
     <t>DamageIncrea</t>
   </si>
   <si>
+    <t>DiRise</t>
+  </si>
+  <si>
     <t>DamageResist</t>
   </si>
   <si>
+    <t>DrRise</t>
+  </si>
+  <si>
     <t>CritRate</t>
   </si>
   <si>
+    <t>CrRise</t>
+  </si>
+  <si>
     <t>CritDamage</t>
   </si>
   <si>
+    <t>CrdRise</t>
+  </si>
+  <si>
     <t>Accuracy</t>
   </si>
   <si>
@@ -122,7 +122,7 @@
     <t>1000</t>
   </si>
   <si>
-    <t>0.1</t>
+    <t>1.0116</t>
   </si>
   <si>
     <t>200</t>
@@ -131,43 +131,16 @@
     <t>5E+5</t>
   </si>
   <si>
-    <t>0.2</t>
-  </si>
-  <si>
-    <t>30000</t>
-  </si>
-  <si>
-    <t>6000</t>
-  </si>
-  <si>
-    <t>1E+7</t>
-  </si>
-  <si>
-    <t>0.3</t>
-  </si>
-  <si>
-    <t>1000000</t>
-  </si>
-  <si>
-    <t>200000</t>
-  </si>
-  <si>
-    <t>6E+9</t>
-  </si>
-  <si>
-    <t>0.4</t>
-  </si>
-  <si>
-    <t>80000000</t>
-  </si>
-  <si>
-    <t>16000000</t>
-  </si>
-  <si>
-    <t>5E+11</t>
-  </si>
-  <si>
-    <t>0.5</t>
+    <t>1.0151</t>
+  </si>
+  <si>
+    <t>1E+8</t>
+  </si>
+  <si>
+    <t>2E+7</t>
+  </si>
+  <si>
+    <t>16E+11</t>
   </si>
 </sst>
 </file>
@@ -180,7 +153,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -199,6 +172,12 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF6897BB"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
@@ -670,137 +649,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -813,9 +792,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1135,7 +1116,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:AA15"/>
+  <dimension ref="C1:AA13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="8.58333333333333" style="1" customWidth="1"/>
@@ -1150,13 +1131,10 @@
     <col min="10" max="10" width="10.1666666666667" style="3" customWidth="1"/>
     <col min="11" max="11" width="15.8333333333333" style="3" customWidth="1"/>
     <col min="12" max="12" width="9.58333333333333" style="3" customWidth="1"/>
-    <col min="13" max="13" width="10.1666666666667" style="3" customWidth="1"/>
-    <col min="14" max="14" width="9.08333333333333" style="3" customWidth="1"/>
+    <col min="13" max="14" width="12" style="1" customWidth="1"/>
     <col min="15" max="16" width="12.1666666666667" style="1" customWidth="1"/>
-    <col min="17" max="17" width="12" style="1" customWidth="1"/>
-    <col min="18" max="18" width="12.1666666666667" style="1" customWidth="1"/>
-    <col min="19" max="19" width="6.375" style="1" customWidth="1"/>
-    <col min="20" max="20" width="10" style="1" customWidth="1"/>
+    <col min="17" max="18" width="8.66666666666667" style="1" customWidth="1"/>
+    <col min="19" max="20" width="10" style="1" customWidth="1"/>
     <col min="21" max="21" width="9.08333333333333" style="1" customWidth="1"/>
     <col min="22" max="22" width="9" style="1" customWidth="1"/>
     <col min="23" max="23" width="7.25" style="1" customWidth="1"/>
@@ -1354,13 +1332,13 @@
         <v>28</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N5" s="4" t="s">
         <v>28</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P5" s="4" t="s">
         <v>28</v>
@@ -1369,25 +1347,25 @@
         <v>26</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="S5" s="4" t="s">
         <v>26</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="U5" s="4" t="s">
         <v>26</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="W5" s="4" t="s">
         <v>26</v>
       </c>
       <c r="X5" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Y5" s="4" t="s">
         <v>26</v>
@@ -1410,24 +1388,24 @@
         <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>200</v>
-      </c>
-      <c r="G6" s="6" t="s">
+        <v>1000</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H6" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="I6" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="J6" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="K6" s="6" t="s">
+      <c r="K6" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="L6" s="6" t="s">
+      <c r="L6" s="8" t="s">
         <v>33</v>
       </c>
       <c r="M6" s="2">
@@ -1443,28 +1421,28 @@
         <v>0</v>
       </c>
       <c r="Q6" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R6" s="2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="S6" s="2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="T6" s="2">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="U6" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="V6" s="2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="W6" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="X6" s="2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="Y6" s="2">
         <v>1</v>
@@ -1484,29 +1462,29 @@
         <v>1</v>
       </c>
       <c r="E7" s="2">
-        <f t="shared" ref="E7:E9" si="0">F6+1</f>
-        <v>201</v>
+        <f>F6+1</f>
+        <v>1001</v>
       </c>
       <c r="F7" s="2">
-        <v>400</v>
-      </c>
-      <c r="G7" s="6" t="s">
+        <v>2000</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="H7" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L7" s="8" t="s">
         <v>33</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="L7" s="6" t="s">
-        <v>37</v>
       </c>
       <c r="M7" s="2">
         <v>0</v>
@@ -1521,28 +1499,32 @@
         <v>0</v>
       </c>
       <c r="Q7" s="2">
-        <v>0</v>
+        <f>Q6+(F6-E6+1)*R6</f>
+        <v>20</v>
       </c>
       <c r="R7" s="2">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="S7" s="2">
-        <v>0</v>
+        <f>S6+(F6-E6+1)*T6</f>
+        <v>100</v>
       </c>
       <c r="T7" s="2">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="U7" s="2">
-        <v>10</v>
+        <f>U6+(F6-E6+1)*V6</f>
+        <v>20</v>
       </c>
       <c r="V7" s="2">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="W7" s="2">
-        <v>10</v>
+        <f>W6+(F6-E6+1)*X6</f>
+        <v>20</v>
       </c>
       <c r="X7" s="2">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="Y7" s="2">
         <v>2</v>
@@ -1551,164 +1533,24 @@
         <v>2</v>
       </c>
       <c r="AA7" s="2">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="3:27">
-      <c r="C8" s="2">
-        <v>3</v>
-      </c>
-      <c r="D8" s="2">
-        <v>1</v>
-      </c>
-      <c r="E8" s="2">
-        <f t="shared" si="0"/>
-        <v>401</v>
-      </c>
-      <c r="F8" s="2">
-        <v>600</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="K8" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="L8" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="M8" s="2">
-        <v>0</v>
-      </c>
-      <c r="N8" s="2">
-        <v>0</v>
-      </c>
-      <c r="O8" s="2">
-        <v>0</v>
-      </c>
-      <c r="P8" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="2">
-        <v>0</v>
-      </c>
-      <c r="R8" s="2">
-        <v>0</v>
-      </c>
-      <c r="S8" s="2">
-        <v>0</v>
-      </c>
-      <c r="T8" s="2">
-        <v>0</v>
-      </c>
-      <c r="U8" s="2">
-        <v>15</v>
-      </c>
-      <c r="V8" s="2">
-        <v>0</v>
-      </c>
-      <c r="W8" s="2">
-        <v>15</v>
-      </c>
-      <c r="X8" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="2">
-        <v>3</v>
-      </c>
-      <c r="Z8" s="2">
-        <v>3</v>
-      </c>
-      <c r="AA8" s="2">
-        <v>0</v>
-      </c>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:27">
-      <c r="C9" s="2">
-        <v>4</v>
-      </c>
-      <c r="D9" s="2">
-        <v>1</v>
-      </c>
-      <c r="E9" s="2">
-        <f t="shared" si="0"/>
-        <v>601</v>
-      </c>
-      <c r="F9" s="2">
-        <v>10000</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="L9" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="M9" s="2">
-        <v>0</v>
-      </c>
-      <c r="N9" s="2">
-        <v>0</v>
-      </c>
-      <c r="O9" s="2">
-        <v>0</v>
-      </c>
-      <c r="P9" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="2">
-        <v>0</v>
-      </c>
-      <c r="R9" s="2">
-        <v>0</v>
-      </c>
-      <c r="S9" s="2">
-        <v>0</v>
-      </c>
-      <c r="T9" s="2">
-        <v>0</v>
-      </c>
-      <c r="U9" s="2">
-        <v>20</v>
-      </c>
-      <c r="V9" s="2">
-        <v>0</v>
-      </c>
-      <c r="W9" s="2">
-        <v>20</v>
-      </c>
-      <c r="X9" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="2">
-        <v>4</v>
-      </c>
-      <c r="Z9" s="2">
-        <v>4</v>
-      </c>
-      <c r="AA9" s="2">
-        <v>0</v>
-      </c>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:27">
       <c r="G10" s="5"/>
@@ -1717,8 +1559,6 @@
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:27">
       <c r="G11" s="5"/>
@@ -1744,27 +1584,9 @@
       <c r="K13" s="5"/>
       <c r="L13" s="5"/>
     </row>
-    <row r="14" s="2" customFormat="1" customHeight="1" spans="3:27">
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-    </row>
-    <row r="15" s="2" customFormat="1" customHeight="1" spans="3:27">
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:AA5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="N3 P3 R3 T3 N4 P4 R4 T4 C5:M5 N5 O5 P5 Q5 R5 S5 T5 U5 V5 W5 X5 Y5:AA5 O3:O4 Q3:Q4 S3:S4 C3:M4 U3:AA4" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/MonsterBabelConfig.xlsx
+++ b/Excel/MonsterBabelConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\legend2\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -119,28 +124,28 @@
     <t>double</t>
   </si>
   <si>
-    <t>1000</t>
+    <t>400</t>
   </si>
   <si>
     <t>1.0116</t>
   </si>
   <si>
-    <t>200</t>
-  </si>
-  <si>
-    <t>5E+5</t>
+    <t>80</t>
+  </si>
+  <si>
+    <t>20E+4</t>
   </si>
   <si>
     <t>1.0151</t>
   </si>
   <si>
-    <t>1E+8</t>
-  </si>
-  <si>
-    <t>2E+7</t>
-  </si>
-  <si>
-    <t>16E+11</t>
+    <t>4E+7</t>
+  </si>
+  <si>
+    <t>8E+6</t>
+  </si>
+  <si>
+    <t>64E+10</t>
   </si>
 </sst>
 </file>
@@ -1586,7 +1591,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="N3 P3 R3 T3 N4 P4 R4 T4 C5:M5 N5 O5 P5 Q5 R5 S5 T5 U5 V5 W5 X5 Y5:AA5 O3:O4 Q3:Q4 S3:S4 C3:M4 U3:AA4" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:AA5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/MonsterBabelConfig.xlsx
+++ b/Excel/MonsterBabelConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -1492,10 +1492,10 @@
         <v>33</v>
       </c>
       <c r="M7" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" s="2">
         <v>0</v>
